--- a/dcf/TSM.xlsx
+++ b/dcf/TSM.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.06742772019955777</v>
+        <v>0.06750399199853613</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.07242772019955777</v>
+        <v>0.07250399199853613</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07742772019955776</v>
+        <v>0.07750399199853612</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.08242772019955777</v>
+        <v>0.08250399199853613</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.08742772019955777</v>
+        <v>0.08750399199853613</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.09242772019955776</v>
+        <v>0.09250399199853612</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.09742772019955777</v>
+        <v>0.09750399199853613</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>12918.95574763939</v>
+        <v>10814.49631945107</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>12424.30674143886</v>
+        <v>10410.51367631718</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>11953.00616466025</v>
+        <v>10025.49563582003</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>11503.82668231406</v>
+        <v>9658.447763018801</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>11075.61133798839</v>
+        <v>9308.432570307359</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>10667.26920018726</v>
+        <v>8974.565997488891</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>10277.77129702487</v>
+        <v>8656.014124859075</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>13833.31633581061</v>
+        <v>11552.57794120111</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>13296.92029802992</v>
+        <v>11114.89899521381</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>12785.95978032475</v>
+        <v>10697.86913963723</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>12299.09413735709</v>
+        <v>10300.40249322601</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>11835.05973663309</v>
+        <v>9921.47547583891</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>11392.66518841046</v>
+        <v>9560.122952482114</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>10970.78689184297</v>
+        <v>9215.434632857419</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>14747.67692398183</v>
+        <v>12290.65956295115</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>14169.53385462097</v>
+        <v>11819.28431411043</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>13618.91339598924</v>
+        <v>11370.24264345443</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>13094.36159240013</v>
+        <v>10942.35722343322</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>12594.50813527779</v>
+        <v>10534.51838137046</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>12118.06117663365</v>
+        <v>10145.67990747534</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>11663.80248666106</v>
+        <v>9774.85514085576</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>15662.03751215305</v>
+        <v>13028.74118470119</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>15042.14741121203</v>
+        <v>12523.66963300705</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>14451.86701165372</v>
+        <v>12042.61614727163</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>13889.62904744317</v>
+        <v>11584.31195364042</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>13353.95653392248</v>
+        <v>11147.56128690201</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>12843.45716485684</v>
+        <v>10731.23686246856</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12356.81808147916</v>
+        <v>10334.2756488541</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>16576.39810032427</v>
+        <v>13766.82280645123</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>15914.76096780308</v>
+        <v>13228.05495190368</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>15284.82062731822</v>
+        <v>12714.98965108883</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>14684.89650248621</v>
+        <v>12226.26668384763</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>14113.40493256718</v>
+        <v>11760.60419243357</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>13568.85315308003</v>
+        <v>11316.79381746178</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>13049.83367629725</v>
+        <v>10893.69615685245</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>17490.75868849549</v>
+        <v>14504.90442820127</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>16787.37452439414</v>
+        <v>13932.4402708003</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>16117.7742429827</v>
+        <v>13387.36315490603</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>15480.16395752925</v>
+        <v>12868.22141405483</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>14872.85333121188</v>
+        <v>12373.64709796512</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>14294.24914130323</v>
+        <v>11902.35077245501</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>13742.84927111535</v>
+        <v>11453.11666485079</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>18405.11927666672</v>
+        <v>15242.98604995131</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17659.9880809852</v>
+        <v>14636.82558969692</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>16950.7278586472</v>
+        <v>14059.73665872323</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>16275.43141257229</v>
+        <v>13510.17614426204</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>15632.30172985658</v>
+        <v>12986.69000349667</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>15019.64512952642</v>
+        <v>12487.90772744823</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>14435.86486593344</v>
+        <v>12012.53717284913</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>434.1600036621094</v>
+        <v>436.6549987792969</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.08242772019955777</v>
+        <v>0.08250399199853613</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.053003016868378</v>
+        <v>1.05774180167132</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>434.1600036621094</v>
+        <v>436.6549987792969</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>13889.62904744317</v>
+        <v>11584.31195364042</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>18653.66860431326</v>
+        <v>15165.56985099866</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>10223.73132671979</v>
+        <v>8754.522610062009</v>
       </c>
     </row>
     <row r="59">
